--- a/consumer-bases/interim/PR_DSS_Reachability.xlsx
+++ b/consumer-bases/interim/PR_DSS_Reachability.xlsx
@@ -484,7 +484,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-23 19:06</t>
+          <t>Generated: 2026-09-30 18:20</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Sources: COSMoS public exports + NCI EVS CT package 2026-03-27.</t>
+          <t>Sources: COSMoS public exports + NCI EVS CT package 2026-09-25.</t>
         </is>
       </c>
     </row>

--- a/consumer-bases/interim/PR_DSS_Reachability.xlsx
+++ b/consumer-bases/interim/PR_DSS_Reachability.xlsx
@@ -484,7 +484,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-30 18:20</t>
+          <t>Generated: 2026-10-01 10:39</t>
         </is>
       </c>
     </row>
